--- a/Lab_4/data/partB/param_optimization_process/v150_k20_s150_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v150_k20_s150_results.xlsx
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -530,16 +530,16 @@
         <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -554,13 +554,13 @@
         <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -570,16 +570,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -594,13 +594,13 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,13 +646,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -677,28 +677,28 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -710,13 +710,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -735,40 +735,40 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>17</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -790,16 +790,16 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
@@ -808,19 +808,19 @@
         <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -842,37 +842,37 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>9</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -882,49 +882,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O9" t="n">
         <v>2</v>
       </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -958,13 +958,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,37 +998,37 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1059,25 +1059,25 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="n">
-        <v>3</v>
-      </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1102,31 +1102,31 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
         <v>5</v>
@@ -1142,49 +1142,49 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
         <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" t="n">
-        <v>23</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1215,25 +1215,25 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,49 +1246,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
         <v>7</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13303,7 +13303,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -14986,7 +14986,7 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15122,7 +15122,7 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15768,7 +15768,7 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16176,7 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16448,7 +16448,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17995,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="C990" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C1026" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18981,7 +18981,7 @@
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19100,7 +19100,7 @@
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19253,7 +19253,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="C1062" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20868,7 +20868,7 @@
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21038,7 +21038,7 @@
       </c>
       <c r="C1161" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21123,7 +21123,7 @@
       </c>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21769,7 +21769,7 @@
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21820,7 +21820,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22500,7 @@
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="C1274" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23180,7 +23180,7 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23214,7 +23214,7 @@
       </c>
       <c r="C1289" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="C1329" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="C1356" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
       </c>
       <c r="C1393" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="C1398" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25135,7 +25135,7 @@
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25220,7 +25220,7 @@
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25543,7 +25543,7 @@
       </c>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25764,7 +25764,7 @@
       </c>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26393,7 +26393,7 @@
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26597,7 +26597,7 @@
       </c>
       <c r="C1488" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
